--- a/public/TPSR_template.xlsx
+++ b/public/TPSR_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\d\magang\simagang\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\web-tpsr\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A3F5B5-6148-4B1A-8C59-AECF5834B5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C944E3-595E-4D34-A4E4-2973BE197A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="42">
   <si>
     <t>Nama Siswa</t>
   </si>
@@ -155,15 +155,39 @@
     <t>5-D</t>
   </si>
   <si>
-    <t>NB: ini hanyalah template, isi dengan data yang anda inginkan</t>
+    <t>NB:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dokumen ini hanya merupakan template. Silakan isi setiap field dengan data yang sesuai dengan kebutuhan. Untuk field Kelas, harap menggantinya dengan nama kelas yang sebenarnya berdasarkan data yang akan diinput. Apabila data kelas yang diinput sudah tersedia dalam sistem, maka data siswa dan penilaiannya akan ditambahkan ke kelas tersebut. Jika data kelas belum tersedia, sistem akan secara otomatis membuat kelas baru beserta data siswa dan penilaiannya sesuai dengan informasi yang diberikan. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mohon untuk tidak mengubah struktur template ini agar proses impor data dapat berjalan dengan baik.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -209,24 +233,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:CC13"/>
+  <dimension ref="A2:CC17"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
@@ -540,132 +571,132 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:81" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:81" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="1" t="s">
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="1" t="s">
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AG3" s="2"/>
-      <c r="AH3" s="2"/>
-      <c r="AI3" s="2"/>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="1" t="s">
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="AO3" s="2"/>
-      <c r="AP3" s="1" t="s">
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3"/>
+      <c r="AN3" s="3"/>
+      <c r="AO3" s="3"/>
+      <c r="AP3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AQ3" s="2"/>
-      <c r="AR3" s="2"/>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2"/>
-      <c r="AU3" s="1" t="s">
+      <c r="AQ3" s="3"/>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3"/>
+      <c r="AT3" s="3"/>
+      <c r="AU3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AV3" s="2"/>
-      <c r="AW3" s="2"/>
-      <c r="AX3" s="2"/>
-      <c r="AY3" s="2"/>
-      <c r="AZ3" s="1" t="s">
+      <c r="AV3" s="3"/>
+      <c r="AW3" s="3"/>
+      <c r="AX3" s="3"/>
+      <c r="AY3" s="3"/>
+      <c r="AZ3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="BA3" s="2"/>
-      <c r="BB3" s="2"/>
-      <c r="BC3" s="2"/>
-      <c r="BD3" s="2"/>
-      <c r="BE3" s="1" t="s">
+      <c r="BA3" s="3"/>
+      <c r="BB3" s="3"/>
+      <c r="BC3" s="3"/>
+      <c r="BD3" s="3"/>
+      <c r="BE3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="BF3" s="2"/>
-      <c r="BG3" s="2"/>
-      <c r="BH3" s="2"/>
-      <c r="BI3" s="2"/>
-      <c r="BJ3" s="1" t="s">
+      <c r="BF3" s="3"/>
+      <c r="BG3" s="3"/>
+      <c r="BH3" s="3"/>
+      <c r="BI3" s="3"/>
+      <c r="BJ3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="BK3" s="2"/>
-      <c r="BL3" s="2"/>
-      <c r="BM3" s="2"/>
-      <c r="BN3" s="2"/>
-      <c r="BO3" s="1" t="s">
+      <c r="BK3" s="3"/>
+      <c r="BL3" s="3"/>
+      <c r="BM3" s="3"/>
+      <c r="BN3" s="3"/>
+      <c r="BO3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="2"/>
-      <c r="BQ3" s="2"/>
-      <c r="BR3" s="2"/>
-      <c r="BS3" s="2"/>
-      <c r="BT3" s="1" t="s">
+      <c r="BP3" s="3"/>
+      <c r="BQ3" s="3"/>
+      <c r="BR3" s="3"/>
+      <c r="BS3" s="3"/>
+      <c r="BT3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BU3" s="2"/>
-      <c r="BV3" s="2"/>
-      <c r="BW3" s="2"/>
-      <c r="BX3" s="2"/>
-      <c r="BY3" s="1" t="s">
+      <c r="BU3" s="3"/>
+      <c r="BV3" s="3"/>
+      <c r="BW3" s="3"/>
+      <c r="BX3" s="3"/>
+      <c r="BY3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="BZ3" s="2"/>
-      <c r="CA3" s="2"/>
-      <c r="CB3" s="2"/>
-      <c r="CC3" s="2"/>
+      <c r="BZ3" s="3"/>
+      <c r="CA3" s="3"/>
+      <c r="CB3" s="3"/>
+      <c r="CC3" s="3"/>
     </row>
     <row r="4" spans="1:81" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3"/>
       <c r="B4" t="s">
         <v>17</v>
       </c>
@@ -2132,13 +2163,85 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:81" x14ac:dyDescent="0.3">
-      <c r="D13" t="s">
+    <row r="13" spans="1:81" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="10" t="s">
         <v>40</v>
       </c>
+      <c r="D13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="C15" s="10"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+    </row>
+    <row r="16" spans="1:81" x14ac:dyDescent="0.3">
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C17" s="10"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="D13:N17"/>
     <mergeCell ref="AF3:AJ3"/>
     <mergeCell ref="L3:P3"/>
     <mergeCell ref="AA3:AE3"/>
@@ -2155,7 +2258,6 @@
     <mergeCell ref="BE3:BI3"/>
     <mergeCell ref="BT3:BX3"/>
     <mergeCell ref="V3:Z3"/>
-    <mergeCell ref="Q3:U3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2170,204 +2272,204 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:161" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3"/>
+      <c r="AO1" s="3"/>
+      <c r="AP1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="2"/>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="2"/>
-      <c r="AY1" s="2"/>
-      <c r="AZ1" s="1" t="s">
+      <c r="AQ1" s="3"/>
+      <c r="AR1" s="3"/>
+      <c r="AS1" s="3"/>
+      <c r="AT1" s="3"/>
+      <c r="AU1" s="3"/>
+      <c r="AV1" s="3"/>
+      <c r="AW1" s="3"/>
+      <c r="AX1" s="3"/>
+      <c r="AY1" s="3"/>
+      <c r="AZ1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="BA1" s="2"/>
-      <c r="BB1" s="2"/>
-      <c r="BC1" s="2"/>
-      <c r="BD1" s="2"/>
-      <c r="BE1" s="2"/>
-      <c r="BF1" s="2"/>
-      <c r="BG1" s="2"/>
-      <c r="BH1" s="2"/>
-      <c r="BI1" s="2"/>
-      <c r="BJ1" s="1" t="s">
+      <c r="BA1" s="3"/>
+      <c r="BB1" s="3"/>
+      <c r="BC1" s="3"/>
+      <c r="BD1" s="3"/>
+      <c r="BE1" s="3"/>
+      <c r="BF1" s="3"/>
+      <c r="BG1" s="3"/>
+      <c r="BH1" s="3"/>
+      <c r="BI1" s="3"/>
+      <c r="BJ1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="BK1" s="2"/>
-      <c r="BL1" s="2"/>
-      <c r="BM1" s="2"/>
-      <c r="BN1" s="2"/>
-      <c r="BO1" s="2"/>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="2"/>
-      <c r="BS1" s="2"/>
-      <c r="BT1" s="1" t="s">
+      <c r="BK1" s="3"/>
+      <c r="BL1" s="3"/>
+      <c r="BM1" s="3"/>
+      <c r="BN1" s="3"/>
+      <c r="BO1" s="3"/>
+      <c r="BP1" s="3"/>
+      <c r="BQ1" s="3"/>
+      <c r="BR1" s="3"/>
+      <c r="BS1" s="3"/>
+      <c r="BT1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="BU1" s="2"/>
-      <c r="BV1" s="2"/>
-      <c r="BW1" s="2"/>
-      <c r="BX1" s="2"/>
-      <c r="BY1" s="2"/>
-      <c r="BZ1" s="2"/>
-      <c r="CA1" s="2"/>
-      <c r="CB1" s="2"/>
-      <c r="CC1" s="2"/>
-      <c r="CD1" s="1" t="s">
+      <c r="BU1" s="3"/>
+      <c r="BV1" s="3"/>
+      <c r="BW1" s="3"/>
+      <c r="BX1" s="3"/>
+      <c r="BY1" s="3"/>
+      <c r="BZ1" s="3"/>
+      <c r="CA1" s="3"/>
+      <c r="CB1" s="3"/>
+      <c r="CC1" s="3"/>
+      <c r="CD1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="CE1" s="2"/>
-      <c r="CF1" s="2"/>
-      <c r="CG1" s="2"/>
-      <c r="CH1" s="2"/>
-      <c r="CI1" s="2"/>
-      <c r="CJ1" s="2"/>
-      <c r="CK1" s="2"/>
-      <c r="CL1" s="2"/>
-      <c r="CM1" s="2"/>
-      <c r="CN1" s="1" t="s">
+      <c r="CE1" s="3"/>
+      <c r="CF1" s="3"/>
+      <c r="CG1" s="3"/>
+      <c r="CH1" s="3"/>
+      <c r="CI1" s="3"/>
+      <c r="CJ1" s="3"/>
+      <c r="CK1" s="3"/>
+      <c r="CL1" s="3"/>
+      <c r="CM1" s="3"/>
+      <c r="CN1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="CO1" s="2"/>
-      <c r="CP1" s="2"/>
-      <c r="CQ1" s="2"/>
-      <c r="CR1" s="2"/>
-      <c r="CS1" s="2"/>
-      <c r="CT1" s="2"/>
-      <c r="CU1" s="2"/>
-      <c r="CV1" s="2"/>
-      <c r="CW1" s="2"/>
-      <c r="CX1" s="1" t="s">
+      <c r="CO1" s="3"/>
+      <c r="CP1" s="3"/>
+      <c r="CQ1" s="3"/>
+      <c r="CR1" s="3"/>
+      <c r="CS1" s="3"/>
+      <c r="CT1" s="3"/>
+      <c r="CU1" s="3"/>
+      <c r="CV1" s="3"/>
+      <c r="CW1" s="3"/>
+      <c r="CX1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="CY1" s="2"/>
-      <c r="CZ1" s="2"/>
-      <c r="DA1" s="2"/>
-      <c r="DB1" s="2"/>
-      <c r="DC1" s="2"/>
-      <c r="DD1" s="2"/>
-      <c r="DE1" s="2"/>
-      <c r="DF1" s="2"/>
-      <c r="DG1" s="2"/>
-      <c r="DH1" s="1" t="s">
+      <c r="CY1" s="3"/>
+      <c r="CZ1" s="3"/>
+      <c r="DA1" s="3"/>
+      <c r="DB1" s="3"/>
+      <c r="DC1" s="3"/>
+      <c r="DD1" s="3"/>
+      <c r="DE1" s="3"/>
+      <c r="DF1" s="3"/>
+      <c r="DG1" s="3"/>
+      <c r="DH1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="DI1" s="2"/>
-      <c r="DJ1" s="2"/>
-      <c r="DK1" s="2"/>
-      <c r="DL1" s="2"/>
-      <c r="DM1" s="2"/>
-      <c r="DN1" s="2"/>
-      <c r="DO1" s="2"/>
-      <c r="DP1" s="2"/>
-      <c r="DQ1" s="2"/>
-      <c r="DR1" s="1" t="s">
+      <c r="DI1" s="3"/>
+      <c r="DJ1" s="3"/>
+      <c r="DK1" s="3"/>
+      <c r="DL1" s="3"/>
+      <c r="DM1" s="3"/>
+      <c r="DN1" s="3"/>
+      <c r="DO1" s="3"/>
+      <c r="DP1" s="3"/>
+      <c r="DQ1" s="3"/>
+      <c r="DR1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="DS1" s="2"/>
-      <c r="DT1" s="2"/>
-      <c r="DU1" s="2"/>
-      <c r="DV1" s="2"/>
-      <c r="DW1" s="2"/>
-      <c r="DX1" s="2"/>
-      <c r="DY1" s="2"/>
-      <c r="DZ1" s="2"/>
-      <c r="EA1" s="2"/>
-      <c r="EB1" s="1" t="s">
+      <c r="DS1" s="3"/>
+      <c r="DT1" s="3"/>
+      <c r="DU1" s="3"/>
+      <c r="DV1" s="3"/>
+      <c r="DW1" s="3"/>
+      <c r="DX1" s="3"/>
+      <c r="DY1" s="3"/>
+      <c r="DZ1" s="3"/>
+      <c r="EA1" s="3"/>
+      <c r="EB1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="EC1" s="2"/>
-      <c r="ED1" s="2"/>
-      <c r="EE1" s="2"/>
-      <c r="EF1" s="2"/>
-      <c r="EG1" s="2"/>
-      <c r="EH1" s="2"/>
-      <c r="EI1" s="2"/>
-      <c r="EJ1" s="2"/>
-      <c r="EK1" s="2"/>
-      <c r="EL1" s="1" t="s">
+      <c r="EC1" s="3"/>
+      <c r="ED1" s="3"/>
+      <c r="EE1" s="3"/>
+      <c r="EF1" s="3"/>
+      <c r="EG1" s="3"/>
+      <c r="EH1" s="3"/>
+      <c r="EI1" s="3"/>
+      <c r="EJ1" s="3"/>
+      <c r="EK1" s="3"/>
+      <c r="EL1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="EM1" s="2"/>
-      <c r="EN1" s="2"/>
-      <c r="EO1" s="2"/>
-      <c r="EP1" s="2"/>
-      <c r="EQ1" s="2"/>
-      <c r="ER1" s="2"/>
-      <c r="ES1" s="2"/>
-      <c r="ET1" s="2"/>
-      <c r="EU1" s="2"/>
-      <c r="EV1" s="1" t="s">
+      <c r="EM1" s="3"/>
+      <c r="EN1" s="3"/>
+      <c r="EO1" s="3"/>
+      <c r="EP1" s="3"/>
+      <c r="EQ1" s="3"/>
+      <c r="ER1" s="3"/>
+      <c r="ES1" s="3"/>
+      <c r="ET1" s="3"/>
+      <c r="EU1" s="3"/>
+      <c r="EV1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="EW1" s="2"/>
-      <c r="EX1" s="2"/>
-      <c r="EY1" s="2"/>
-      <c r="EZ1" s="2"/>
-      <c r="FA1" s="2"/>
-      <c r="FB1" s="2"/>
-      <c r="FC1" s="2"/>
-      <c r="FD1" s="2"/>
-      <c r="FE1" s="2"/>
+      <c r="EW1" s="3"/>
+      <c r="EX1" s="3"/>
+      <c r="EY1" s="3"/>
+      <c r="EZ1" s="3"/>
+      <c r="FA1" s="3"/>
+      <c r="FB1" s="3"/>
+      <c r="FC1" s="3"/>
+      <c r="FD1" s="3"/>
+      <c r="FE1" s="3"/>
     </row>
     <row r="2" spans="1:161" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
+      <c r="A2" s="3"/>
       <c r="B2" t="s">
         <v>27</v>
       </c>
@@ -6076,6 +6178,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="L1:U1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="EL1:EU1"/>
+    <mergeCell ref="EB1:EK1"/>
+    <mergeCell ref="B1:K1"/>
     <mergeCell ref="EV1:FE1"/>
     <mergeCell ref="V1:AE1"/>
     <mergeCell ref="AF1:AO1"/>
@@ -6088,11 +6195,6 @@
     <mergeCell ref="BT1:CC1"/>
     <mergeCell ref="AP1:AY1"/>
     <mergeCell ref="BJ1:BS1"/>
-    <mergeCell ref="L1:U1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="EL1:EU1"/>
-    <mergeCell ref="EB1:EK1"/>
-    <mergeCell ref="B1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/TPSR_template.xlsx
+++ b/public/TPSR_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\web-tpsr\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C944E3-595E-4D34-A4E4-2973BE197A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D17866-4C4D-44CB-8964-FD6663CB8B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -195,7 +195,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -220,6 +220,72 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -233,31 +299,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:CC17"/>
+  <dimension ref="A2:CE17"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
@@ -568,9 +654,11 @@
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="82" max="82" width="13" customWidth="1"/>
+    <col min="83" max="83" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -578,367 +666,371 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:81" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="2" t="s">
+      <c r="B3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="2" t="s">
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="2" t="s">
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="2" t="s">
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="17"/>
+      <c r="AJ3" s="17"/>
+      <c r="AK3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="2" t="s">
+      <c r="AL3" s="19"/>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="19"/>
+      <c r="AO3" s="19"/>
+      <c r="AP3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="AQ3" s="3"/>
-      <c r="AR3" s="3"/>
-      <c r="AS3" s="3"/>
-      <c r="AT3" s="3"/>
-      <c r="AU3" s="2" t="s">
+      <c r="AQ3" s="17"/>
+      <c r="AR3" s="17"/>
+      <c r="AS3" s="17"/>
+      <c r="AT3" s="17"/>
+      <c r="AU3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="AV3" s="3"/>
-      <c r="AW3" s="3"/>
-      <c r="AX3" s="3"/>
-      <c r="AY3" s="3"/>
-      <c r="AZ3" s="2" t="s">
+      <c r="AV3" s="19"/>
+      <c r="AW3" s="19"/>
+      <c r="AX3" s="19"/>
+      <c r="AY3" s="19"/>
+      <c r="AZ3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="BA3" s="3"/>
-      <c r="BB3" s="3"/>
-      <c r="BC3" s="3"/>
-      <c r="BD3" s="3"/>
-      <c r="BE3" s="2" t="s">
+      <c r="BA3" s="17"/>
+      <c r="BB3" s="17"/>
+      <c r="BC3" s="17"/>
+      <c r="BD3" s="17"/>
+      <c r="BE3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="BF3" s="3"/>
-      <c r="BG3" s="3"/>
-      <c r="BH3" s="3"/>
-      <c r="BI3" s="3"/>
-      <c r="BJ3" s="2" t="s">
+      <c r="BF3" s="19"/>
+      <c r="BG3" s="19"/>
+      <c r="BH3" s="19"/>
+      <c r="BI3" s="19"/>
+      <c r="BJ3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="BK3" s="3"/>
-      <c r="BL3" s="3"/>
-      <c r="BM3" s="3"/>
-      <c r="BN3" s="3"/>
-      <c r="BO3" s="2" t="s">
+      <c r="BK3" s="17"/>
+      <c r="BL3" s="17"/>
+      <c r="BM3" s="17"/>
+      <c r="BN3" s="17"/>
+      <c r="BO3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="3"/>
-      <c r="BQ3" s="3"/>
-      <c r="BR3" s="3"/>
-      <c r="BS3" s="3"/>
-      <c r="BT3" s="2" t="s">
+      <c r="BP3" s="19"/>
+      <c r="BQ3" s="19"/>
+      <c r="BR3" s="19"/>
+      <c r="BS3" s="19"/>
+      <c r="BT3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="BU3" s="3"/>
-      <c r="BV3" s="3"/>
-      <c r="BW3" s="3"/>
-      <c r="BX3" s="3"/>
-      <c r="BY3" s="2" t="s">
+      <c r="BU3" s="17"/>
+      <c r="BV3" s="17"/>
+      <c r="BW3" s="17"/>
+      <c r="BX3" s="17"/>
+      <c r="BY3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="BZ3" s="3"/>
-      <c r="CA3" s="3"/>
-      <c r="CB3" s="3"/>
-      <c r="CC3" s="3"/>
+      <c r="BZ3" s="19"/>
+      <c r="CA3" s="19"/>
+      <c r="CB3" s="19"/>
+      <c r="CC3" s="19"/>
+      <c r="CD3" s="12"/>
+      <c r="CE3" s="13"/>
     </row>
-    <row r="4" spans="1:81" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" t="s">
+    <row r="4" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="A4" s="19"/>
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="U4" t="s">
+      <c r="U4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AA4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AD4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AE4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AF4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AG4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AH4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AI4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AJ4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AK4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AL4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AM4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AN4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AO4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AP4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AQ4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AR4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AS4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AT4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AW4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AX4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AY4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="AZ4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BA4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BB4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BC4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BD4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BE4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BF4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BG4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BH4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BI4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BJ4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BK4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BL4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="BO4" t="s">
+      <c r="BO4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="BP4" t="s">
+      <c r="BP4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="BQ4" t="s">
+      <c r="BQ4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="BR4" t="s">
+      <c r="BR4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="BS4" t="s">
+      <c r="BS4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="BT4" t="s">
+      <c r="BT4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="BU4" t="s">
+      <c r="BU4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="BV4" t="s">
+      <c r="BV4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="BW4" t="s">
+      <c r="BW4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="BX4" t="s">
+      <c r="BX4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="BY4" t="s">
+      <c r="BY4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="BZ4" t="s">
+      <c r="BZ4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="CA4" t="s">
+      <c r="CA4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="CB4" t="s">
+      <c r="CB4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="CC4" t="s">
+      <c r="CC4" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="CD4" s="12"/>
+      <c r="CE4" s="13"/>
     </row>
-    <row r="5" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1183,7 +1275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1428,7 +1520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1673,7 +1765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1918,7 +2010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:81" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:83" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -2163,88 +2255,82 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:81" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="10" t="s">
+    <row r="13" spans="1:83" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
     </row>
-    <row r="14" spans="1:81" x14ac:dyDescent="0.3">
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
+    <row r="14" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="C14" s="14"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
     </row>
-    <row r="15" spans="1:81" x14ac:dyDescent="0.3">
-      <c r="C15" s="10"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
+    <row r="15" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="C15" s="14"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
     </row>
-    <row r="16" spans="1:81" x14ac:dyDescent="0.3">
-      <c r="C16" s="10"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
+    <row r="16" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="C16" s="14"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C17" s="10"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="D13:N17"/>
-    <mergeCell ref="AF3:AJ3"/>
-    <mergeCell ref="L3:P3"/>
-    <mergeCell ref="AA3:AE3"/>
+  <mergeCells count="21">
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="BY3:CC3"/>
     <mergeCell ref="B3:F3"/>
@@ -2258,6 +2344,14 @@
     <mergeCell ref="BE3:BI3"/>
     <mergeCell ref="BT3:BX3"/>
     <mergeCell ref="V3:Z3"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="CD3:CD4"/>
+    <mergeCell ref="CE3:CE4"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="D13:N17"/>
+    <mergeCell ref="AF3:AJ3"/>
+    <mergeCell ref="L3:P3"/>
+    <mergeCell ref="AA3:AE3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2268,686 +2362,846 @@
   <dimension ref="A1:FE7"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="10" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="10" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="10" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="10" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="10" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="10" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="10" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="10" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="10" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="147" max="147" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="148" max="148" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="10" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="151" max="151" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="152" max="152" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="156" max="156" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="158" max="158" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="159" max="159" width="10" bestFit="1" customWidth="1"/>
+    <col min="160" max="160" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:161" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="3"/>
-      <c r="AI1" s="3"/>
-      <c r="AJ1" s="3"/>
-      <c r="AK1" s="3"/>
-      <c r="AL1" s="3"/>
-      <c r="AM1" s="3"/>
-      <c r="AN1" s="3"/>
-      <c r="AO1" s="3"/>
-      <c r="AP1" s="2" t="s">
+      <c r="B1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="25"/>
+      <c r="AK1" s="25"/>
+      <c r="AL1" s="25"/>
+      <c r="AM1" s="25"/>
+      <c r="AN1" s="25"/>
+      <c r="AO1" s="25"/>
+      <c r="AP1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AQ1" s="3"/>
-      <c r="AR1" s="3"/>
-      <c r="AS1" s="3"/>
-      <c r="AT1" s="3"/>
-      <c r="AU1" s="3"/>
-      <c r="AV1" s="3"/>
-      <c r="AW1" s="3"/>
-      <c r="AX1" s="3"/>
-      <c r="AY1" s="3"/>
-      <c r="AZ1" s="2" t="s">
+      <c r="AQ1" s="21"/>
+      <c r="AR1" s="21"/>
+      <c r="AS1" s="21"/>
+      <c r="AT1" s="21"/>
+      <c r="AU1" s="21"/>
+      <c r="AV1" s="21"/>
+      <c r="AW1" s="21"/>
+      <c r="AX1" s="21"/>
+      <c r="AY1" s="21"/>
+      <c r="AZ1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="BA1" s="3"/>
-      <c r="BB1" s="3"/>
-      <c r="BC1" s="3"/>
-      <c r="BD1" s="3"/>
-      <c r="BE1" s="3"/>
-      <c r="BF1" s="3"/>
-      <c r="BG1" s="3"/>
-      <c r="BH1" s="3"/>
-      <c r="BI1" s="3"/>
-      <c r="BJ1" s="2" t="s">
+      <c r="BA1" s="23"/>
+      <c r="BB1" s="23"/>
+      <c r="BC1" s="23"/>
+      <c r="BD1" s="23"/>
+      <c r="BE1" s="23"/>
+      <c r="BF1" s="23"/>
+      <c r="BG1" s="23"/>
+      <c r="BH1" s="23"/>
+      <c r="BI1" s="23"/>
+      <c r="BJ1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="BK1" s="3"/>
-      <c r="BL1" s="3"/>
-      <c r="BM1" s="3"/>
-      <c r="BN1" s="3"/>
-      <c r="BO1" s="3"/>
-      <c r="BP1" s="3"/>
-      <c r="BQ1" s="3"/>
-      <c r="BR1" s="3"/>
-      <c r="BS1" s="3"/>
-      <c r="BT1" s="2" t="s">
+      <c r="BK1" s="25"/>
+      <c r="BL1" s="25"/>
+      <c r="BM1" s="25"/>
+      <c r="BN1" s="25"/>
+      <c r="BO1" s="25"/>
+      <c r="BP1" s="25"/>
+      <c r="BQ1" s="25"/>
+      <c r="BR1" s="25"/>
+      <c r="BS1" s="25"/>
+      <c r="BT1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="BU1" s="3"/>
-      <c r="BV1" s="3"/>
-      <c r="BW1" s="3"/>
-      <c r="BX1" s="3"/>
-      <c r="BY1" s="3"/>
-      <c r="BZ1" s="3"/>
-      <c r="CA1" s="3"/>
-      <c r="CB1" s="3"/>
-      <c r="CC1" s="3"/>
-      <c r="CD1" s="2" t="s">
+      <c r="BU1" s="21"/>
+      <c r="BV1" s="21"/>
+      <c r="BW1" s="21"/>
+      <c r="BX1" s="21"/>
+      <c r="BY1" s="21"/>
+      <c r="BZ1" s="21"/>
+      <c r="CA1" s="21"/>
+      <c r="CB1" s="21"/>
+      <c r="CC1" s="21"/>
+      <c r="CD1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="CE1" s="3"/>
-      <c r="CF1" s="3"/>
-      <c r="CG1" s="3"/>
-      <c r="CH1" s="3"/>
-      <c r="CI1" s="3"/>
-      <c r="CJ1" s="3"/>
-      <c r="CK1" s="3"/>
-      <c r="CL1" s="3"/>
-      <c r="CM1" s="3"/>
-      <c r="CN1" s="2" t="s">
+      <c r="CE1" s="23"/>
+      <c r="CF1" s="23"/>
+      <c r="CG1" s="23"/>
+      <c r="CH1" s="23"/>
+      <c r="CI1" s="23"/>
+      <c r="CJ1" s="23"/>
+      <c r="CK1" s="23"/>
+      <c r="CL1" s="23"/>
+      <c r="CM1" s="23"/>
+      <c r="CN1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="CO1" s="3"/>
-      <c r="CP1" s="3"/>
-      <c r="CQ1" s="3"/>
-      <c r="CR1" s="3"/>
-      <c r="CS1" s="3"/>
-      <c r="CT1" s="3"/>
-      <c r="CU1" s="3"/>
-      <c r="CV1" s="3"/>
-      <c r="CW1" s="3"/>
-      <c r="CX1" s="2" t="s">
+      <c r="CO1" s="25"/>
+      <c r="CP1" s="25"/>
+      <c r="CQ1" s="25"/>
+      <c r="CR1" s="25"/>
+      <c r="CS1" s="25"/>
+      <c r="CT1" s="25"/>
+      <c r="CU1" s="25"/>
+      <c r="CV1" s="25"/>
+      <c r="CW1" s="25"/>
+      <c r="CX1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="CY1" s="3"/>
-      <c r="CZ1" s="3"/>
-      <c r="DA1" s="3"/>
-      <c r="DB1" s="3"/>
-      <c r="DC1" s="3"/>
-      <c r="DD1" s="3"/>
-      <c r="DE1" s="3"/>
-      <c r="DF1" s="3"/>
-      <c r="DG1" s="3"/>
-      <c r="DH1" s="2" t="s">
+      <c r="CY1" s="21"/>
+      <c r="CZ1" s="21"/>
+      <c r="DA1" s="21"/>
+      <c r="DB1" s="21"/>
+      <c r="DC1" s="21"/>
+      <c r="DD1" s="21"/>
+      <c r="DE1" s="21"/>
+      <c r="DF1" s="21"/>
+      <c r="DG1" s="21"/>
+      <c r="DH1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="DI1" s="3"/>
-      <c r="DJ1" s="3"/>
-      <c r="DK1" s="3"/>
-      <c r="DL1" s="3"/>
-      <c r="DM1" s="3"/>
-      <c r="DN1" s="3"/>
-      <c r="DO1" s="3"/>
-      <c r="DP1" s="3"/>
-      <c r="DQ1" s="3"/>
-      <c r="DR1" s="2" t="s">
+      <c r="DI1" s="23"/>
+      <c r="DJ1" s="23"/>
+      <c r="DK1" s="23"/>
+      <c r="DL1" s="23"/>
+      <c r="DM1" s="23"/>
+      <c r="DN1" s="23"/>
+      <c r="DO1" s="23"/>
+      <c r="DP1" s="23"/>
+      <c r="DQ1" s="23"/>
+      <c r="DR1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="DS1" s="3"/>
-      <c r="DT1" s="3"/>
-      <c r="DU1" s="3"/>
-      <c r="DV1" s="3"/>
-      <c r="DW1" s="3"/>
-      <c r="DX1" s="3"/>
-      <c r="DY1" s="3"/>
-      <c r="DZ1" s="3"/>
-      <c r="EA1" s="3"/>
-      <c r="EB1" s="2" t="s">
+      <c r="DS1" s="25"/>
+      <c r="DT1" s="25"/>
+      <c r="DU1" s="25"/>
+      <c r="DV1" s="25"/>
+      <c r="DW1" s="25"/>
+      <c r="DX1" s="25"/>
+      <c r="DY1" s="25"/>
+      <c r="DZ1" s="25"/>
+      <c r="EA1" s="25"/>
+      <c r="EB1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="EC1" s="3"/>
-      <c r="ED1" s="3"/>
-      <c r="EE1" s="3"/>
-      <c r="EF1" s="3"/>
-      <c r="EG1" s="3"/>
-      <c r="EH1" s="3"/>
-      <c r="EI1" s="3"/>
-      <c r="EJ1" s="3"/>
-      <c r="EK1" s="3"/>
-      <c r="EL1" s="2" t="s">
+      <c r="EC1" s="21"/>
+      <c r="ED1" s="21"/>
+      <c r="EE1" s="21"/>
+      <c r="EF1" s="21"/>
+      <c r="EG1" s="21"/>
+      <c r="EH1" s="21"/>
+      <c r="EI1" s="21"/>
+      <c r="EJ1" s="21"/>
+      <c r="EK1" s="21"/>
+      <c r="EL1" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="EM1" s="3"/>
-      <c r="EN1" s="3"/>
-      <c r="EO1" s="3"/>
-      <c r="EP1" s="3"/>
-      <c r="EQ1" s="3"/>
-      <c r="ER1" s="3"/>
-      <c r="ES1" s="3"/>
-      <c r="ET1" s="3"/>
-      <c r="EU1" s="3"/>
-      <c r="EV1" s="2" t="s">
+      <c r="EM1" s="23"/>
+      <c r="EN1" s="23"/>
+      <c r="EO1" s="23"/>
+      <c r="EP1" s="23"/>
+      <c r="EQ1" s="23"/>
+      <c r="ER1" s="23"/>
+      <c r="ES1" s="23"/>
+      <c r="ET1" s="23"/>
+      <c r="EU1" s="23"/>
+      <c r="EV1" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="EW1" s="3"/>
-      <c r="EX1" s="3"/>
-      <c r="EY1" s="3"/>
-      <c r="EZ1" s="3"/>
-      <c r="FA1" s="3"/>
-      <c r="FB1" s="3"/>
-      <c r="FC1" s="3"/>
-      <c r="FD1" s="3"/>
-      <c r="FE1" s="3"/>
+      <c r="EW1" s="25"/>
+      <c r="EX1" s="25"/>
+      <c r="EY1" s="25"/>
+      <c r="EZ1" s="25"/>
+      <c r="FA1" s="25"/>
+      <c r="FB1" s="25"/>
+      <c r="FC1" s="25"/>
+      <c r="FD1" s="25"/>
+      <c r="FE1" s="25"/>
     </row>
     <row r="2" spans="1:161" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" t="s">
+      <c r="A2" s="17"/>
+      <c r="B2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="Z2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AE2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AG2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AH2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AI2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AK2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AL2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AN2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AO2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AP2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AQ2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AS2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AT2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AU2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AV2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AW2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AX2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AY2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AZ2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BA2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BB2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BC2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BD2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BE2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BF2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BG2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BH2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BI2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BJ2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BK2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BL2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BM2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BN2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BO2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BP2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BQ2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BR2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BS2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BT2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="BU2" t="s">
+      <c r="BU2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="BV2" t="s">
+      <c r="BV2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BW2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BX2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BY2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="BZ2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CA2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CB2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CC2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CD2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CE2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CF2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CG2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CH2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CI2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CJ2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CK2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CL2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CM2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CN2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CO2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CP2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CQ2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CR2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CS2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CT2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CU2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CV2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CW2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CX2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CY2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="CZ2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DA2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DB2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DC2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DD2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DE2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DF2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DG2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="DH2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="DI2" t="s">
+      <c r="DI2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="DJ2" t="s">
+      <c r="DJ2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="DK2" t="s">
+      <c r="DK2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="DL2" t="s">
+      <c r="DL2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="DM2" t="s">
+      <c r="DM2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="DN2" t="s">
+      <c r="DN2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="DO2" t="s">
+      <c r="DO2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="DP2" t="s">
+      <c r="DP2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="DQ2" t="s">
+      <c r="DQ2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="DR2" t="s">
+      <c r="DR2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="DS2" t="s">
+      <c r="DS2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="DT2" t="s">
+      <c r="DT2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="DU2" t="s">
+      <c r="DU2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="DV2" t="s">
+      <c r="DV2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="DW2" t="s">
+      <c r="DW2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="DX2" t="s">
+      <c r="DX2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="DY2" t="s">
+      <c r="DY2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="DZ2" t="s">
+      <c r="DZ2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="EA2" t="s">
+      <c r="EA2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="EB2" t="s">
+      <c r="EB2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="EC2" t="s">
+      <c r="EC2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="ED2" t="s">
+      <c r="ED2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="EE2" t="s">
+      <c r="EE2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="EF2" t="s">
+      <c r="EF2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="EG2" t="s">
+      <c r="EG2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="EH2" t="s">
+      <c r="EH2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="EI2" t="s">
+      <c r="EI2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="EJ2" t="s">
+      <c r="EJ2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="EK2" t="s">
+      <c r="EK2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="EL2" t="s">
+      <c r="EL2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="EM2" t="s">
+      <c r="EM2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="EN2" t="s">
+      <c r="EN2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="EO2" t="s">
+      <c r="EO2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="EP2" t="s">
+      <c r="EP2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="EQ2" t="s">
+      <c r="EQ2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="ER2" t="s">
+      <c r="ER2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="ES2" t="s">
+      <c r="ES2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="ET2" t="s">
+      <c r="ET2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="EU2" t="s">
+      <c r="EU2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="EV2" t="s">
+      <c r="EV2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="EW2" t="s">
+      <c r="EW2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="EX2" t="s">
+      <c r="EX2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="EY2" t="s">
+      <c r="EY2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="EZ2" t="s">
+      <c r="EZ2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="FA2" t="s">
+      <c r="FA2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="FB2" t="s">
+      <c r="FB2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="FC2" t="s">
+      <c r="FC2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="FD2" t="s">
+      <c r="FD2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="FE2" t="s">
+      <c r="FE2" s="4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -6178,11 +6432,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="L1:U1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="EL1:EU1"/>
-    <mergeCell ref="EB1:EK1"/>
-    <mergeCell ref="B1:K1"/>
     <mergeCell ref="EV1:FE1"/>
     <mergeCell ref="V1:AE1"/>
     <mergeCell ref="AF1:AO1"/>
@@ -6195,6 +6444,11 @@
     <mergeCell ref="BT1:CC1"/>
     <mergeCell ref="AP1:AY1"/>
     <mergeCell ref="BJ1:BS1"/>
+    <mergeCell ref="L1:U1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="EL1:EU1"/>
+    <mergeCell ref="EB1:EK1"/>
+    <mergeCell ref="B1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6223,37 +6477,37 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="10" t="s">
         <v>36</v>
       </c>
     </row>
@@ -6273,7 +6527,7 @@
         <f>AVERAGE(Resume_Karakter!D3,Resume_Karakter!N3,Resume_Karakter!X3,Resume_Karakter!AH3,Resume_Karakter!AR3,Resume_Karakter!BB3,Resume_Karakter!BL3,Resume_Karakter!BV3,Resume_Karakter!CF3,Resume_Karakter!CP3,Resume_Karakter!CZ3,Resume_Karakter!DJ3,Resume_Karakter!DT3,Resume_Karakter!ED3,Resume_Karakter!EN3,Resume_Karakter!EX3)</f>
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="11">
         <f>AVERAGE(Resume_Karakter!E3,Resume_Karakter!O3,Resume_Karakter!Y3,Resume_Karakter!AI3,Resume_Karakter!AS3,Resume_Karakter!BC3,Resume_Karakter!BM3,Resume_Karakter!BW3,Resume_Karakter!CG3,Resume_Karakter!CQ3,Resume_Karakter!DA3,Resume_Karakter!DK3,Resume_Karakter!DU3,Resume_Karakter!EE3,Resume_Karakter!EO3,Resume_Karakter!EY3)</f>
         <v>3</v>
       </c>
